--- a/outputs/daily/hr_rankings_2026-10-05.xlsx
+++ b/outputs/daily/hr_rankings_2026-10-05.xlsx
@@ -760,7 +760,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -784,7 +784,7 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>69.40000000000001</v>
+        <v>69</v>
       </c>
       <c r="M2" t="inlineStr">
         <is>
@@ -808,7 +808,7 @@
         <v>54.7</v>
       </c>
       <c r="R2" t="n">
-        <v>40.6</v>
+        <v>38.1</v>
       </c>
       <c r="S2" t="n">
         <v>94.90000000000001</v>
@@ -994,12 +994,12 @@
       </c>
       <c r="BG2" t="inlineStr">
         <is>
-          <t>In From LF</t>
+          <t>In From CF</t>
         </is>
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>62</t>
+          <t>61</t>
         </is>
       </c>
       <c r="BI2" t="inlineStr">
@@ -1064,7 +1064,7 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>58.3</v>
+        <v>59</v>
       </c>
       <c r="M3" t="inlineStr">
         <is>
@@ -1078,7 +1078,7 @@
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
+          <t>Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P3" t="n">
@@ -1091,7 +1091,7 @@
         <v>41.1</v>
       </c>
       <c r="S3" t="n">
-        <v>90.40000000000001</v>
+        <v>94.90000000000001</v>
       </c>
       <c r="T3" t="n">
         <v>80</v>
@@ -1101,39 +1101,35 @@
       </c>
       <c r="V3" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W3" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="Y3" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr"/>
       <c r="AC3" t="inlineStr">
         <is>
           <t>H:2026 P:2026/2025</t>
@@ -1348,7 +1344,7 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>57.9</v>
+        <v>58.5</v>
       </c>
       <c r="M4" t="inlineStr">
         <is>
@@ -1362,7 +1358,7 @@
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
+          <t>Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P4" t="n">
@@ -1375,7 +1371,7 @@
         <v>41.1</v>
       </c>
       <c r="S4" t="n">
-        <v>88.7</v>
+        <v>93.2</v>
       </c>
       <c r="T4" t="n">
         <v>80</v>
@@ -1385,39 +1381,35 @@
       </c>
       <c r="V4" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W4" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="Y4" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr"/>
       <c r="AC4" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -1608,7 +1600,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -1632,7 +1624,7 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>55.8</v>
+        <v>55.4</v>
       </c>
       <c r="M5" t="inlineStr">
         <is>
@@ -1656,7 +1648,7 @@
         <v>54.7</v>
       </c>
       <c r="R5" t="n">
-        <v>40.6</v>
+        <v>38.1</v>
       </c>
       <c r="S5" t="n">
         <v>96.59999999999999</v>
@@ -1842,12 +1834,12 @@
       </c>
       <c r="BG5" t="inlineStr">
         <is>
-          <t>In From LF</t>
+          <t>In From CF</t>
         </is>
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>62</t>
+          <t>61</t>
         </is>
       </c>
       <c r="BI5" t="inlineStr">
@@ -1888,7 +1880,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -1912,7 +1904,7 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>55.4</v>
+        <v>55</v>
       </c>
       <c r="M6" t="inlineStr">
         <is>
@@ -1936,7 +1928,7 @@
         <v>40.1</v>
       </c>
       <c r="R6" t="n">
-        <v>40.6</v>
+        <v>38.1</v>
       </c>
       <c r="S6" t="n">
         <v>94.90000000000001</v>
@@ -2122,12 +2114,12 @@
       </c>
       <c r="BG6" t="inlineStr">
         <is>
-          <t>In From LF</t>
+          <t>In From CF</t>
         </is>
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>62</t>
+          <t>61</t>
         </is>
       </c>
       <c r="BI6" t="inlineStr">
@@ -2168,7 +2160,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -2192,7 +2184,7 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>54.8</v>
+        <v>54.5</v>
       </c>
       <c r="M7" t="inlineStr">
         <is>
@@ -2216,7 +2208,7 @@
         <v>54.7</v>
       </c>
       <c r="R7" t="n">
-        <v>40.6</v>
+        <v>38.1</v>
       </c>
       <c r="S7" t="n">
         <v>100</v>
@@ -2402,12 +2394,12 @@
       </c>
       <c r="BG7" t="inlineStr">
         <is>
-          <t>In From LF</t>
+          <t>In From CF</t>
         </is>
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>62</t>
+          <t>61</t>
         </is>
       </c>
       <c r="BI7" t="inlineStr">
@@ -3008,7 +3000,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -3032,7 +3024,7 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>51.8</v>
+        <v>51.4</v>
       </c>
       <c r="M10" t="inlineStr">
         <is>
@@ -3056,7 +3048,7 @@
         <v>54.7</v>
       </c>
       <c r="R10" t="n">
-        <v>40.6</v>
+        <v>38.1</v>
       </c>
       <c r="S10" t="n">
         <v>86.40000000000001</v>
@@ -3242,12 +3234,12 @@
       </c>
       <c r="BG10" t="inlineStr">
         <is>
-          <t>In From LF</t>
+          <t>In From CF</t>
         </is>
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>62</t>
+          <t>61</t>
         </is>
       </c>
       <c r="BI10" t="inlineStr">
@@ -3268,7 +3260,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Luis Garcia</t>
+          <t>Luis García Jr.</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -3312,7 +3304,7 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>50.6</v>
+        <v>51.2</v>
       </c>
       <c r="M11" t="inlineStr">
         <is>
@@ -3326,7 +3318,7 @@
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
+          <t>Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P11" t="n">
@@ -3339,7 +3331,7 @@
         <v>41.1</v>
       </c>
       <c r="S11" t="n">
-        <v>92.09999999999999</v>
+        <v>96.59999999999999</v>
       </c>
       <c r="T11" t="n">
         <v>80</v>
@@ -3349,39 +3341,35 @@
       </c>
       <c r="V11" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W11" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X11" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="Y11" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr"/>
       <c r="AC11" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -3852,7 +3840,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -3876,7 +3864,7 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>49.1</v>
+        <v>48.8</v>
       </c>
       <c r="M13" t="inlineStr">
         <is>
@@ -3900,7 +3888,7 @@
         <v>54.7</v>
       </c>
       <c r="R13" t="n">
-        <v>40.6</v>
+        <v>38.1</v>
       </c>
       <c r="S13" t="n">
         <v>44.8</v>
@@ -4086,12 +4074,12 @@
       </c>
       <c r="BG13" t="inlineStr">
         <is>
-          <t>In From LF</t>
+          <t>In From CF</t>
         </is>
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>62</t>
+          <t>61</t>
         </is>
       </c>
       <c r="BI13" t="inlineStr">
@@ -4132,7 +4120,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -4156,7 +4144,7 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>48.1</v>
+        <v>47.8</v>
       </c>
       <c r="M14" t="inlineStr">
         <is>
@@ -4180,7 +4168,7 @@
         <v>40.1</v>
       </c>
       <c r="R14" t="n">
-        <v>40.6</v>
+        <v>38.1</v>
       </c>
       <c r="S14" t="n">
         <v>96.59999999999999</v>
@@ -4366,12 +4354,12 @@
       </c>
       <c r="BG14" t="inlineStr">
         <is>
-          <t>In From LF</t>
+          <t>In From CF</t>
         </is>
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>62</t>
+          <t>61</t>
         </is>
       </c>
       <c r="BI14" t="inlineStr">
@@ -4412,7 +4400,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -4436,7 +4424,7 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>47.8</v>
+        <v>47.5</v>
       </c>
       <c r="M15" t="inlineStr">
         <is>
@@ -4460,7 +4448,7 @@
         <v>54.7</v>
       </c>
       <c r="R15" t="n">
-        <v>40.6</v>
+        <v>38.1</v>
       </c>
       <c r="S15" t="n">
         <v>93.2</v>
@@ -4646,12 +4634,12 @@
       </c>
       <c r="BG15" t="inlineStr">
         <is>
-          <t>In From LF</t>
+          <t>In From CF</t>
         </is>
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>62</t>
+          <t>61</t>
         </is>
       </c>
       <c r="BI15" t="inlineStr">
@@ -4667,24 +4655,24 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>650490</t>
+          <t>665862</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Yandy Díaz</t>
+          <t>Jazz Chisholm Jr.</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
+          <t>NYY</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
           <t>TB</t>
         </is>
       </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>NYY</t>
-        </is>
-      </c>
       <c r="F16" t="inlineStr">
         <is>
           <t>2026-10-06T00:00:00Z</t>
@@ -4697,17 +4685,17 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>6</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>Cam Schlittler</t>
+          <t>Freddy Peralta</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>693645</t>
+          <t>642547</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -4716,7 +4704,7 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>46.3</v>
+        <v>46.7</v>
       </c>
       <c r="M16" t="inlineStr">
         <is>
@@ -4730,11 +4718,11 @@
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>Premium Lineup Spot</t>
+          <t>Strong Barrel, Platoon Edge</t>
         </is>
       </c>
       <c r="P16" t="n">
-        <v>41</v>
+        <v>42.2</v>
       </c>
       <c r="Q16" t="n">
         <v>33.4</v>
@@ -4743,13 +4731,13 @@
         <v>41.1</v>
       </c>
       <c r="S16" t="n">
-        <v>93.2</v>
+        <v>76.2</v>
       </c>
       <c r="T16" t="n">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="U16" t="n">
-        <v>20.9</v>
+        <v>14.6</v>
       </c>
       <c r="V16" t="inlineStr">
         <is>
@@ -4763,7 +4751,7 @@
       </c>
       <c r="X16" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>6</t>
         </is>
       </c>
       <c r="Y16" t="inlineStr">
@@ -4801,12 +4789,12 @@
       </c>
       <c r="AH16" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AI16" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>23</t>
         </is>
       </c>
       <c r="AJ16" t="inlineStr">
@@ -4816,12 +4804,12 @@
       </c>
       <c r="AK16" t="inlineStr">
         <is>
-          <t>Last 7 games: 7/27, 0 HR</t>
+          <t>Last 7 games: 5/23, 0 HR</t>
         </is>
       </c>
       <c r="AL16" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 7.6% barrel, 13.6 HR allowed</t>
+          <t>platoon edge; pitcher baseline 6.8% barrel, 22.4 HR allowed</t>
         </is>
       </c>
       <c r="AM16" t="inlineStr">
@@ -4831,97 +4819,97 @@
       </c>
       <c r="AN16" t="inlineStr">
         <is>
-          <t>7.46</t>
+          <t>10.24</t>
         </is>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
-          <t>49.42</t>
+          <t>42.95</t>
         </is>
       </c>
       <c r="AP16" t="inlineStr">
         <is>
-          <t>91.53</t>
+          <t>89.98</t>
         </is>
       </c>
       <c r="AQ16" t="inlineStr">
         <is>
-          <t>103.1694</t>
+          <t>100.4248</t>
         </is>
       </c>
       <c r="AR16" t="inlineStr">
         <is>
-          <t>0.4453</t>
+          <t>0.4005</t>
         </is>
       </c>
       <c r="AS16" t="inlineStr">
         <is>
-          <t>0.1621</t>
+          <t>0.1791</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr">
         <is>
-          <t>0.3484</t>
+          <t>0.3093</t>
         </is>
       </c>
       <c r="AU16" t="inlineStr">
         <is>
-          <t>73.5</t>
+          <t>73.2</t>
         </is>
       </c>
       <c r="AV16" t="inlineStr">
         <is>
-          <t>37.37</t>
+          <t>32.25</t>
         </is>
       </c>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>23.46</t>
+          <t>50.3</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>19.65</t>
+          <t>30.19</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr">
         <is>
-          <t>22.9</t>
+          <t>22.6</t>
         </is>
       </c>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>0.1617</t>
+          <t>0.1893</t>
         </is>
       </c>
       <c r="BA16" t="inlineStr">
         <is>
-          <t>7.57</t>
+          <t>6.85</t>
         </is>
       </c>
       <c r="BB16" t="inlineStr">
         <is>
-          <t>38.87</t>
+          <t>36.39</t>
         </is>
       </c>
       <c r="BC16" t="inlineStr">
         <is>
-          <t>88.58</t>
+          <t>87.72</t>
         </is>
       </c>
       <c r="BD16" t="inlineStr">
         <is>
-          <t>0.3434</t>
+          <t>0.368</t>
         </is>
       </c>
       <c r="BE16" t="inlineStr">
         <is>
-          <t>0.1302</t>
+          <t>0.1417</t>
         </is>
       </c>
       <c r="BF16" t="inlineStr">
         <is>
-          <t>25.76</t>
+          <t>28.41</t>
         </is>
       </c>
       <c r="BG16" t="inlineStr">
@@ -4947,12 +4935,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>665862</t>
+          <t>641355</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Jazz Chisholm</t>
+          <t>Cody Bellinger</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -4977,7 +4965,7 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -4996,7 +4984,7 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>46.1</v>
+        <v>46.4</v>
       </c>
       <c r="M17" t="inlineStr">
         <is>
@@ -5010,11 +4998,11 @@
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel, Platoon Edge</t>
+          <t>Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P17" t="n">
-        <v>42.2</v>
+        <v>30.5</v>
       </c>
       <c r="Q17" t="n">
         <v>33.4</v>
@@ -5023,49 +5011,45 @@
         <v>41.1</v>
       </c>
       <c r="S17" t="n">
-        <v>71.7</v>
+        <v>100</v>
       </c>
       <c r="T17" t="n">
         <v>80</v>
       </c>
       <c r="U17" t="n">
-        <v>14.6</v>
+        <v>18.3</v>
       </c>
       <c r="V17" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X17" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W17" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X17" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="Y17" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr"/>
       <c r="AC17" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -5085,22 +5069,22 @@
       </c>
       <c r="AH17" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AI17" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>28</t>
         </is>
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AK17" t="inlineStr">
         <is>
-          <t>Last 7 games: 5/23, 0 HR</t>
+          <t>Last 7 games: 3/28, 1 HR</t>
         </is>
       </c>
       <c r="AL17" t="inlineStr">
@@ -5115,67 +5099,67 @@
       </c>
       <c r="AN17" t="inlineStr">
         <is>
-          <t>10.24</t>
+          <t>6.87</t>
         </is>
       </c>
       <c r="AO17" t="inlineStr">
         <is>
-          <t>42.95</t>
+          <t>37.83</t>
         </is>
       </c>
       <c r="AP17" t="inlineStr">
         <is>
-          <t>89.98</t>
+          <t>88.93</t>
         </is>
       </c>
       <c r="AQ17" t="inlineStr">
         <is>
-          <t>100.4248</t>
+          <t>98.5475</t>
         </is>
       </c>
       <c r="AR17" t="inlineStr">
         <is>
-          <t>0.4005</t>
+          <t>0.4152</t>
         </is>
       </c>
       <c r="AS17" t="inlineStr">
         <is>
-          <t>0.1791</t>
+          <t>0.1505</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr">
         <is>
-          <t>0.3093</t>
+          <t>0.3314</t>
         </is>
       </c>
       <c r="AU17" t="inlineStr">
         <is>
-          <t>73.2</t>
+          <t>69.96</t>
         </is>
       </c>
       <c r="AV17" t="inlineStr">
         <is>
-          <t>32.25</t>
+          <t>4.82</t>
         </is>
       </c>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>50.3</t>
+          <t>44.36</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>30.19</t>
+          <t>31.85</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr">
         <is>
-          <t>22.6</t>
+          <t>20.6</t>
         </is>
       </c>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>0.1893</t>
+          <t>0.1779</t>
         </is>
       </c>
       <c r="BA17" t="inlineStr">
@@ -5231,27 +5215,27 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>608070</t>
+          <t>650490</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>José Ramírez</t>
+          <t>Yandy Díaz</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>CLE</t>
+          <t>TB</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>CWS</t>
+          <t>NYY</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2026-10-05T21:00:00Z</t>
+          <t>2026-10-06T00:00:00Z</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -5261,26 +5245,26 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>Anthony Kay</t>
+          <t>Cam Schlittler</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>641743</t>
+          <t>693645</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>R</t>
         </is>
       </c>
       <c r="L18" t="n">
-        <v>45.7</v>
+        <v>46.3</v>
       </c>
       <c r="M18" t="inlineStr">
         <is>
@@ -5294,26 +5278,26 @@
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>Premium Lineup Spot, Platoon Edge</t>
+          <t>Premium Lineup Spot</t>
         </is>
       </c>
       <c r="P18" t="n">
-        <v>25.8</v>
+        <v>41</v>
       </c>
       <c r="Q18" t="n">
-        <v>38.1</v>
+        <v>33.4</v>
       </c>
       <c r="R18" t="n">
-        <v>40.6</v>
+        <v>41.1</v>
       </c>
       <c r="S18" t="n">
-        <v>100</v>
+        <v>93.2</v>
       </c>
       <c r="T18" t="n">
-        <v>75</v>
+        <v>50</v>
       </c>
       <c r="U18" t="n">
-        <v>23.4</v>
+        <v>20.9</v>
       </c>
       <c r="V18" t="inlineStr">
         <is>
@@ -5327,7 +5311,7 @@
       </c>
       <c r="X18" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="Y18" t="inlineStr">
@@ -5348,7 +5332,7 @@
       <c r="AB18" t="inlineStr"/>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AD18" t="inlineStr"/>
@@ -5365,12 +5349,12 @@
       </c>
       <c r="AH18" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AI18" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>27</t>
         </is>
       </c>
       <c r="AJ18" t="inlineStr">
@@ -5380,12 +5364,12 @@
       </c>
       <c r="AK18" t="inlineStr">
         <is>
-          <t>Last 7 games: 8/29, 0 HR</t>
+          <t>Last 7 games: 7/27, 0 HR</t>
         </is>
       </c>
       <c r="AL18" t="inlineStr">
         <is>
-          <t>switch hitter; pitcher baseline 8.1% barrel, 21.0 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 7.6% barrel, 13.6 HR allowed</t>
         </is>
       </c>
       <c r="AM18" t="inlineStr">
@@ -5395,112 +5379,112 @@
       </c>
       <c r="AN18" t="inlineStr">
         <is>
-          <t>4.97</t>
+          <t>7.46</t>
         </is>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
-          <t>38.26</t>
+          <t>49.42</t>
         </is>
       </c>
       <c r="AP18" t="inlineStr">
         <is>
-          <t>88.69</t>
+          <t>91.53</t>
         </is>
       </c>
       <c r="AQ18" t="inlineStr">
         <is>
-          <t>99.2749</t>
+          <t>103.1694</t>
         </is>
       </c>
       <c r="AR18" t="inlineStr">
         <is>
-          <t>0.4075</t>
+          <t>0.4453</t>
         </is>
       </c>
       <c r="AS18" t="inlineStr">
         <is>
-          <t>0.1361</t>
+          <t>0.1621</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr">
         <is>
-          <t>0.3301</t>
+          <t>0.3484</t>
         </is>
       </c>
       <c r="AU18" t="inlineStr">
         <is>
-          <t>70.41</t>
+          <t>73.5</t>
         </is>
       </c>
       <c r="AV18" t="inlineStr">
         <is>
-          <t>12.84</t>
+          <t>37.37</t>
         </is>
       </c>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>50.41</t>
+          <t>23.46</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>27.87</t>
+          <t>19.65</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr">
         <is>
-          <t>17.4</t>
+          <t>22.9</t>
         </is>
       </c>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>0.1591</t>
+          <t>0.1617</t>
         </is>
       </c>
       <c r="BA18" t="inlineStr">
         <is>
-          <t>8.1</t>
+          <t>7.57</t>
         </is>
       </c>
       <c r="BB18" t="inlineStr">
         <is>
-          <t>38.9</t>
+          <t>38.87</t>
         </is>
       </c>
       <c r="BC18" t="inlineStr">
         <is>
-          <t>88.3</t>
+          <t>88.58</t>
         </is>
       </c>
       <c r="BD18" t="inlineStr">
         <is>
-          <t>0.419</t>
+          <t>0.3434</t>
         </is>
       </c>
       <c r="BE18" t="inlineStr">
         <is>
-          <t>0.153</t>
+          <t>0.1302</t>
         </is>
       </c>
       <c r="BF18" t="inlineStr">
         <is>
-          <t>22.0</t>
+          <t>25.76</t>
         </is>
       </c>
       <c r="BG18" t="inlineStr">
         <is>
-          <t>In From LF</t>
+          <t>None</t>
         </is>
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>62</t>
+          <t>72</t>
         </is>
       </c>
       <c r="BI18" t="inlineStr">
         <is>
-          <t>Progressive Field</t>
+          <t>Tropicana Field</t>
         </is>
       </c>
       <c r="BJ18" t="inlineStr"/>
@@ -5511,12 +5495,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>641355</t>
+          <t>663757</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Cody Bellinger</t>
+          <t>Trent Grisham</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -5541,7 +5525,7 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>7</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -5560,7 +5544,7 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>45.7</v>
+        <v>46</v>
       </c>
       <c r="M19" t="inlineStr">
         <is>
@@ -5574,11 +5558,11 @@
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot, Platoon Edge</t>
+          <t>Strong Barrel, Platoon Edge</t>
         </is>
       </c>
       <c r="P19" t="n">
-        <v>30.5</v>
+        <v>47.4</v>
       </c>
       <c r="Q19" t="n">
         <v>33.4</v>
@@ -5587,49 +5571,45 @@
         <v>41.1</v>
       </c>
       <c r="S19" t="n">
-        <v>95.5</v>
+        <v>64.3</v>
       </c>
       <c r="T19" t="n">
         <v>80</v>
       </c>
       <c r="U19" t="n">
-        <v>18.3</v>
+        <v>0</v>
       </c>
       <c r="V19" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X19" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W19" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X19" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="Y19" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z19" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB19" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr"/>
       <c r="AC19" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -5649,22 +5629,22 @@
       </c>
       <c r="AH19" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AI19" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>20</t>
         </is>
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AK19" t="inlineStr">
         <is>
-          <t>Last 7 games: 3/28, 1 HR</t>
+          <t>Last 7 games: 2/20, 0 HR</t>
         </is>
       </c>
       <c r="AL19" t="inlineStr">
@@ -5679,67 +5659,67 @@
       </c>
       <c r="AN19" t="inlineStr">
         <is>
-          <t>6.87</t>
+          <t>10.98</t>
         </is>
       </c>
       <c r="AO19" t="inlineStr">
         <is>
-          <t>37.83</t>
+          <t>45.63</t>
         </is>
       </c>
       <c r="AP19" t="inlineStr">
         <is>
-          <t>88.93</t>
+          <t>90.75</t>
         </is>
       </c>
       <c r="AQ19" t="inlineStr">
         <is>
-          <t>98.5475</t>
+          <t>100.7514</t>
         </is>
       </c>
       <c r="AR19" t="inlineStr">
         <is>
-          <t>0.4152</t>
+          <t>0.4497</t>
         </is>
       </c>
       <c r="AS19" t="inlineStr">
         <is>
-          <t>0.1505</t>
+          <t>0.2038</t>
         </is>
       </c>
       <c r="AT19" t="inlineStr">
         <is>
-          <t>0.3314</t>
+          <t>0.3469</t>
         </is>
       </c>
       <c r="AU19" t="inlineStr">
         <is>
-          <t>69.96</t>
+          <t>70.79</t>
         </is>
       </c>
       <c r="AV19" t="inlineStr">
         <is>
-          <t>4.82</t>
+          <t>9.51</t>
         </is>
       </c>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>44.36</t>
+          <t>45.42</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>31.85</t>
+          <t>31.05</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr">
         <is>
-          <t>20.6</t>
+          <t>22.8</t>
         </is>
       </c>
       <c r="AZ19" t="inlineStr">
         <is>
-          <t>0.1779</t>
+          <t>0.1975</t>
         </is>
       </c>
       <c r="BA19" t="inlineStr">
@@ -5795,56 +5775,56 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>663757</t>
+          <t>608070</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Trent Grisham</t>
+          <t>José Ramírez</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NYY</t>
+          <t>CLE</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>TB</t>
+          <t>CWS</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>2026-10-06T00:00:00Z</t>
+          <t>2026-10-05T21:00:00Z</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>Freddy Peralta</t>
+          <t>Anthony Kay</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>642547</t>
+          <t>641743</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>L</t>
         </is>
       </c>
       <c r="L20" t="n">
-        <v>45.4</v>
+        <v>45.3</v>
       </c>
       <c r="M20" t="inlineStr">
         <is>
@@ -5858,65 +5838,61 @@
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel, Platoon Edge</t>
+          <t>Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P20" t="n">
-        <v>47.4</v>
+        <v>25.8</v>
       </c>
       <c r="Q20" t="n">
-        <v>33.4</v>
+        <v>38.1</v>
       </c>
       <c r="R20" t="n">
-        <v>41.1</v>
+        <v>38.1</v>
       </c>
       <c r="S20" t="n">
-        <v>59.8</v>
+        <v>100</v>
       </c>
       <c r="T20" t="n">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="U20" t="n">
-        <v>0</v>
+        <v>23.4</v>
       </c>
       <c r="V20" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X20" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z20" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W20" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X20" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="Y20" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z20" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB20" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB20" t="inlineStr"/>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026/2025</t>
+          <t>H:2026/2025 P:2026</t>
         </is>
       </c>
       <c r="AD20" t="inlineStr"/>
@@ -5933,12 +5909,12 @@
       </c>
       <c r="AH20" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AI20" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>29</t>
         </is>
       </c>
       <c r="AJ20" t="inlineStr">
@@ -5948,12 +5924,12 @@
       </c>
       <c r="AK20" t="inlineStr">
         <is>
-          <t>Last 7 games: 2/20, 0 HR</t>
+          <t>Last 7 games: 8/29, 0 HR</t>
         </is>
       </c>
       <c r="AL20" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 6.8% barrel, 22.4 HR allowed</t>
+          <t>switch hitter; pitcher baseline 8.1% barrel, 21.0 HR allowed</t>
         </is>
       </c>
       <c r="AM20" t="inlineStr">
@@ -5963,112 +5939,112 @@
       </c>
       <c r="AN20" t="inlineStr">
         <is>
-          <t>10.98</t>
+          <t>4.97</t>
         </is>
       </c>
       <c r="AO20" t="inlineStr">
         <is>
-          <t>45.63</t>
+          <t>38.26</t>
         </is>
       </c>
       <c r="AP20" t="inlineStr">
         <is>
-          <t>90.75</t>
+          <t>88.69</t>
         </is>
       </c>
       <c r="AQ20" t="inlineStr">
         <is>
-          <t>100.7514</t>
+          <t>99.2749</t>
         </is>
       </c>
       <c r="AR20" t="inlineStr">
         <is>
-          <t>0.4497</t>
+          <t>0.4075</t>
         </is>
       </c>
       <c r="AS20" t="inlineStr">
         <is>
-          <t>0.2038</t>
+          <t>0.1361</t>
         </is>
       </c>
       <c r="AT20" t="inlineStr">
         <is>
-          <t>0.3469</t>
+          <t>0.3301</t>
         </is>
       </c>
       <c r="AU20" t="inlineStr">
         <is>
-          <t>70.79</t>
+          <t>70.41</t>
         </is>
       </c>
       <c r="AV20" t="inlineStr">
         <is>
-          <t>9.51</t>
+          <t>12.84</t>
         </is>
       </c>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>45.42</t>
+          <t>50.41</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>31.05</t>
+          <t>27.87</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr">
         <is>
-          <t>22.8</t>
+          <t>17.4</t>
         </is>
       </c>
       <c r="AZ20" t="inlineStr">
         <is>
-          <t>0.1975</t>
+          <t>0.1591</t>
         </is>
       </c>
       <c r="BA20" t="inlineStr">
         <is>
-          <t>6.85</t>
+          <t>8.1</t>
         </is>
       </c>
       <c r="BB20" t="inlineStr">
         <is>
-          <t>36.39</t>
+          <t>38.9</t>
         </is>
       </c>
       <c r="BC20" t="inlineStr">
         <is>
-          <t>87.72</t>
+          <t>88.3</t>
         </is>
       </c>
       <c r="BD20" t="inlineStr">
         <is>
-          <t>0.368</t>
+          <t>0.419</t>
         </is>
       </c>
       <c r="BE20" t="inlineStr">
         <is>
-          <t>0.1417</t>
+          <t>0.153</t>
         </is>
       </c>
       <c r="BF20" t="inlineStr">
         <is>
-          <t>28.41</t>
+          <t>22.0</t>
         </is>
       </c>
       <c r="BG20" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>In From CF</t>
         </is>
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>72</t>
+          <t>61</t>
         </is>
       </c>
       <c r="BI20" t="inlineStr">
         <is>
-          <t>Tropicana Field</t>
+          <t>Progressive Field</t>
         </is>
       </c>
       <c r="BJ20" t="inlineStr"/>
@@ -6104,7 +6080,7 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -6128,7 +6104,7 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>44.8</v>
+        <v>44.5</v>
       </c>
       <c r="M21" t="inlineStr">
         <is>
@@ -6152,7 +6128,7 @@
         <v>53.5</v>
       </c>
       <c r="R21" t="n">
-        <v>40.6</v>
+        <v>38.1</v>
       </c>
       <c r="S21" t="n">
         <v>64.3</v>
@@ -6338,12 +6314,12 @@
       </c>
       <c r="BG21" t="inlineStr">
         <is>
-          <t>In From LF</t>
+          <t>In From CF</t>
         </is>
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>62</t>
+          <t>61</t>
         </is>
       </c>
       <c r="BI21" t="inlineStr">
@@ -6384,7 +6360,7 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -6408,7 +6384,7 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>44.8</v>
+        <v>44.4</v>
       </c>
       <c r="M22" t="inlineStr">
         <is>
@@ -6432,7 +6408,7 @@
         <v>40.1</v>
       </c>
       <c r="R22" t="n">
-        <v>40.6</v>
+        <v>38.1</v>
       </c>
       <c r="S22" t="n">
         <v>86.40000000000001</v>
@@ -6618,12 +6594,12 @@
       </c>
       <c r="BG22" t="inlineStr">
         <is>
-          <t>In From LF</t>
+          <t>In From CF</t>
         </is>
       </c>
       <c r="BH22" t="inlineStr">
         <is>
-          <t>62</t>
+          <t>61</t>
         </is>
       </c>
       <c r="BI22" t="inlineStr">
@@ -6688,7 +6664,7 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>43.8</v>
+        <v>44.4</v>
       </c>
       <c r="M23" t="inlineStr">
         <is>
@@ -6702,7 +6678,7 @@
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P23" t="n">
@@ -6715,7 +6691,7 @@
         <v>41.1</v>
       </c>
       <c r="S23" t="n">
-        <v>47.9</v>
+        <v>52.4</v>
       </c>
       <c r="T23" t="n">
         <v>80</v>
@@ -6725,39 +6701,35 @@
       </c>
       <c r="V23" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X23" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z23" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W23" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X23" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="Y23" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z23" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB23" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB23" t="inlineStr"/>
       <c r="AC23" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -6972,7 +6944,7 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>43.4</v>
+        <v>44</v>
       </c>
       <c r="M24" t="inlineStr">
         <is>
@@ -6986,7 +6958,7 @@
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P24" t="n">
@@ -6999,7 +6971,7 @@
         <v>41.1</v>
       </c>
       <c r="S24" t="n">
-        <v>40.2</v>
+        <v>44.8</v>
       </c>
       <c r="T24" t="n">
         <v>80</v>
@@ -7009,39 +6981,35 @@
       </c>
       <c r="V24" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X24" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z24" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W24" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X24" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="Y24" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z24" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB24" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB24" t="inlineStr"/>
       <c r="AC24" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -7212,7 +7180,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>George Lombard</t>
+          <t>George Lombard Jr.</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -7256,7 +7224,7 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>43.1</v>
+        <v>43.7</v>
       </c>
       <c r="M25" t="inlineStr">
         <is>
@@ -7270,7 +7238,7 @@
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>Projected Lineup, Hot Hitter/Streak</t>
+          <t>Hot Hitter/Streak</t>
         </is>
       </c>
       <c r="P25" t="n">
@@ -7283,7 +7251,7 @@
         <v>41.1</v>
       </c>
       <c r="S25" t="n">
-        <v>81.90000000000001</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="T25" t="n">
         <v>50</v>
@@ -7293,39 +7261,35 @@
       </c>
       <c r="V25" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X25" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z25" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W25" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X25" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="Y25" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z25" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB25" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB25" t="inlineStr"/>
       <c r="AC25" t="inlineStr">
         <is>
           <t>H:2026 P:2026/2025</t>
@@ -7516,7 +7480,7 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -7540,7 +7504,7 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>42.4</v>
+        <v>42.1</v>
       </c>
       <c r="M26" t="inlineStr">
         <is>
@@ -7564,7 +7528,7 @@
         <v>38.1</v>
       </c>
       <c r="R26" t="n">
-        <v>40.6</v>
+        <v>38.1</v>
       </c>
       <c r="S26" t="n">
         <v>52.4</v>
@@ -7750,12 +7714,12 @@
       </c>
       <c r="BG26" t="inlineStr">
         <is>
-          <t>In From LF</t>
+          <t>In From CF</t>
         </is>
       </c>
       <c r="BH26" t="inlineStr">
         <is>
-          <t>62</t>
+          <t>61</t>
         </is>
       </c>
       <c r="BI26" t="inlineStr">
@@ -7796,7 +7760,7 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -7820,7 +7784,7 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>42</v>
+        <v>41.7</v>
       </c>
       <c r="M27" t="inlineStr">
         <is>
@@ -7844,7 +7808,7 @@
         <v>38.1</v>
       </c>
       <c r="R27" t="n">
-        <v>40.6</v>
+        <v>38.1</v>
       </c>
       <c r="S27" t="n">
         <v>76.2</v>
@@ -8030,12 +7994,12 @@
       </c>
       <c r="BG27" t="inlineStr">
         <is>
-          <t>In From LF</t>
+          <t>In From CF</t>
         </is>
       </c>
       <c r="BH27" t="inlineStr">
         <is>
-          <t>62</t>
+          <t>61</t>
         </is>
       </c>
       <c r="BI27" t="inlineStr">
@@ -8076,7 +8040,7 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -8100,7 +8064,7 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>41.8</v>
+        <v>41.4</v>
       </c>
       <c r="M28" t="inlineStr">
         <is>
@@ -8124,7 +8088,7 @@
         <v>54.7</v>
       </c>
       <c r="R28" t="n">
-        <v>40.6</v>
+        <v>38.1</v>
       </c>
       <c r="S28" t="n">
         <v>76.2</v>
@@ -8310,12 +8274,12 @@
       </c>
       <c r="BG28" t="inlineStr">
         <is>
-          <t>In From LF</t>
+          <t>In From CF</t>
         </is>
       </c>
       <c r="BH28" t="inlineStr">
         <is>
-          <t>62</t>
+          <t>61</t>
         </is>
       </c>
       <c r="BI28" t="inlineStr">
@@ -8356,7 +8320,7 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -8380,7 +8344,7 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>39.3</v>
+        <v>38.9</v>
       </c>
       <c r="M29" t="inlineStr">
         <is>
@@ -8404,7 +8368,7 @@
         <v>54.7</v>
       </c>
       <c r="R29" t="n">
-        <v>40.6</v>
+        <v>38.1</v>
       </c>
       <c r="S29" t="n">
         <v>52.4</v>
@@ -8590,12 +8554,12 @@
       </c>
       <c r="BG29" t="inlineStr">
         <is>
-          <t>In From LF</t>
+          <t>In From CF</t>
         </is>
       </c>
       <c r="BH29" t="inlineStr">
         <is>
-          <t>62</t>
+          <t>61</t>
         </is>
       </c>
       <c r="BI29" t="inlineStr">
@@ -8916,7 +8880,7 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -8940,7 +8904,7 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>36.7</v>
+        <v>36.4</v>
       </c>
       <c r="M31" t="inlineStr">
         <is>
@@ -8964,7 +8928,7 @@
         <v>40.1</v>
       </c>
       <c r="R31" t="n">
-        <v>40.6</v>
+        <v>38.1</v>
       </c>
       <c r="S31" t="n">
         <v>64.3</v>
@@ -9150,12 +9114,12 @@
       </c>
       <c r="BG31" t="inlineStr">
         <is>
-          <t>In From LF</t>
+          <t>In From CF</t>
         </is>
       </c>
       <c r="BH31" t="inlineStr">
         <is>
-          <t>62</t>
+          <t>61</t>
         </is>
       </c>
       <c r="BI31" t="inlineStr">
@@ -9171,12 +9135,12 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>680757</t>
+          <t>677587</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Steven Kwan</t>
+          <t>Brayan Rocchio</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -9196,12 +9160,12 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>9</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
@@ -9220,7 +9184,7 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>36.4</v>
+        <v>36.1</v>
       </c>
       <c r="M32" t="inlineStr">
         <is>
@@ -9234,26 +9198,26 @@
       </c>
       <c r="O32" t="inlineStr">
         <is>
-          <t>Premium Lineup Spot</t>
+          <t>Platoon Edge, Hot Hitter/Streak</t>
         </is>
       </c>
       <c r="P32" t="n">
-        <v>2.9</v>
+        <v>13.7</v>
       </c>
       <c r="Q32" t="n">
-        <v>40.1</v>
+        <v>38.1</v>
       </c>
       <c r="R32" t="n">
-        <v>40.6</v>
+        <v>38.1</v>
       </c>
       <c r="S32" t="n">
-        <v>93.2</v>
+        <v>44.8</v>
       </c>
       <c r="T32" t="n">
-        <v>50</v>
+        <v>75</v>
       </c>
       <c r="U32" t="n">
-        <v>43.1</v>
+        <v>72.7</v>
       </c>
       <c r="V32" t="inlineStr">
         <is>
@@ -9267,7 +9231,7 @@
       </c>
       <c r="X32" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>9</t>
         </is>
       </c>
       <c r="Y32" t="inlineStr">
@@ -9305,27 +9269,27 @@
       </c>
       <c r="AH32" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>9</t>
         </is>
       </c>
       <c r="AI32" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>25</t>
         </is>
       </c>
       <c r="AJ32" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AK32" t="inlineStr">
         <is>
-          <t>Contact streak: 11/27 over last 7 games</t>
+          <t>Hot streak: 2 HR in last 7 games</t>
         </is>
       </c>
       <c r="AL32" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 8.1% barrel, 21.0 HR allowed</t>
+          <t>switch hitter; pitcher baseline 8.1% barrel, 21.0 HR allowed</t>
         </is>
       </c>
       <c r="AM32" t="inlineStr">
@@ -9335,67 +9299,67 @@
       </c>
       <c r="AN32" t="inlineStr">
         <is>
-          <t>0.85</t>
+          <t>3.02</t>
         </is>
       </c>
       <c r="AO32" t="inlineStr">
         <is>
-          <t>13.14</t>
+          <t>31.65</t>
         </is>
       </c>
       <c r="AP32" t="inlineStr">
         <is>
-          <t>84.59</t>
+          <t>87.3</t>
         </is>
       </c>
       <c r="AQ32" t="inlineStr">
         <is>
-          <t>92.8164</t>
+          <t>97.253</t>
         </is>
       </c>
       <c r="AR32" t="inlineStr">
         <is>
-          <t>0.3499</t>
+          <t>0.3524</t>
         </is>
       </c>
       <c r="AS32" t="inlineStr">
         <is>
-          <t>0.0741</t>
+          <t>0.1067</t>
         </is>
       </c>
       <c r="AT32" t="inlineStr">
         <is>
-          <t>0.3233</t>
+          <t>0.2943</t>
         </is>
       </c>
       <c r="AU32" t="inlineStr">
         <is>
-          <t>62.73</t>
+          <t>69.86</t>
         </is>
       </c>
       <c r="AV32" t="inlineStr">
         <is>
-          <t>0.45</t>
+          <t>6.52</t>
         </is>
       </c>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>27.81</t>
+          <t>43.71</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>23.44</t>
+          <t>25.23</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr">
         <is>
-          <t>5.4</t>
+          <t>12.0</t>
         </is>
       </c>
       <c r="AZ32" t="inlineStr">
         <is>
-          <t>0.0775</t>
+          <t>0.1287</t>
         </is>
       </c>
       <c r="BA32" t="inlineStr">
@@ -9430,12 +9394,12 @@
       </c>
       <c r="BG32" t="inlineStr">
         <is>
-          <t>In From LF</t>
+          <t>In From CF</t>
         </is>
       </c>
       <c r="BH32" t="inlineStr">
         <is>
-          <t>62</t>
+          <t>61</t>
         </is>
       </c>
       <c r="BI32" t="inlineStr">
@@ -9451,12 +9415,12 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>677587</t>
+          <t>680757</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Brayan Rocchio</t>
+          <t>Steven Kwan</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -9476,12 +9440,12 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
@@ -9500,7 +9464,7 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>36.4</v>
+        <v>36</v>
       </c>
       <c r="M33" t="inlineStr">
         <is>
@@ -9514,26 +9478,26 @@
       </c>
       <c r="O33" t="inlineStr">
         <is>
-          <t>Platoon Edge, Hot Hitter/Streak</t>
+          <t>Premium Lineup Spot</t>
         </is>
       </c>
       <c r="P33" t="n">
-        <v>13.7</v>
+        <v>2.9</v>
       </c>
       <c r="Q33" t="n">
+        <v>40.1</v>
+      </c>
+      <c r="R33" t="n">
         <v>38.1</v>
       </c>
-      <c r="R33" t="n">
-        <v>40.6</v>
-      </c>
       <c r="S33" t="n">
-        <v>44.8</v>
+        <v>93.2</v>
       </c>
       <c r="T33" t="n">
-        <v>75</v>
+        <v>50</v>
       </c>
       <c r="U33" t="n">
-        <v>72.7</v>
+        <v>43.1</v>
       </c>
       <c r="V33" t="inlineStr">
         <is>
@@ -9547,7 +9511,7 @@
       </c>
       <c r="X33" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>1</t>
         </is>
       </c>
       <c r="Y33" t="inlineStr">
@@ -9585,27 +9549,27 @@
       </c>
       <c r="AH33" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>11</t>
         </is>
       </c>
       <c r="AI33" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>27</t>
         </is>
       </c>
       <c r="AJ33" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AK33" t="inlineStr">
         <is>
-          <t>Hot streak: 2 HR in last 7 games</t>
+          <t>Contact streak: 11/27 over last 7 games</t>
         </is>
       </c>
       <c r="AL33" t="inlineStr">
         <is>
-          <t>switch hitter; pitcher baseline 8.1% barrel, 21.0 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 8.1% barrel, 21.0 HR allowed</t>
         </is>
       </c>
       <c r="AM33" t="inlineStr">
@@ -9615,67 +9579,67 @@
       </c>
       <c r="AN33" t="inlineStr">
         <is>
-          <t>3.02</t>
+          <t>0.85</t>
         </is>
       </c>
       <c r="AO33" t="inlineStr">
         <is>
-          <t>31.65</t>
+          <t>13.14</t>
         </is>
       </c>
       <c r="AP33" t="inlineStr">
         <is>
-          <t>87.3</t>
+          <t>84.59</t>
         </is>
       </c>
       <c r="AQ33" t="inlineStr">
         <is>
-          <t>97.253</t>
+          <t>92.8164</t>
         </is>
       </c>
       <c r="AR33" t="inlineStr">
         <is>
-          <t>0.3524</t>
+          <t>0.3499</t>
         </is>
       </c>
       <c r="AS33" t="inlineStr">
         <is>
-          <t>0.1067</t>
+          <t>0.0741</t>
         </is>
       </c>
       <c r="AT33" t="inlineStr">
         <is>
-          <t>0.2943</t>
+          <t>0.3233</t>
         </is>
       </c>
       <c r="AU33" t="inlineStr">
         <is>
-          <t>69.86</t>
+          <t>62.73</t>
         </is>
       </c>
       <c r="AV33" t="inlineStr">
         <is>
-          <t>6.52</t>
+          <t>0.45</t>
         </is>
       </c>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>43.71</t>
+          <t>27.81</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>25.23</t>
+          <t>23.44</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr">
         <is>
-          <t>12.0</t>
+          <t>5.4</t>
         </is>
       </c>
       <c r="AZ33" t="inlineStr">
         <is>
-          <t>0.1287</t>
+          <t>0.0775</t>
         </is>
       </c>
       <c r="BA33" t="inlineStr">
@@ -9710,12 +9674,12 @@
       </c>
       <c r="BG33" t="inlineStr">
         <is>
-          <t>In From LF</t>
+          <t>In From CF</t>
         </is>
       </c>
       <c r="BH33" t="inlineStr">
         <is>
-          <t>62</t>
+          <t>61</t>
         </is>
       </c>
       <c r="BI33" t="inlineStr">
@@ -11202,7 +11166,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -11226,7 +11190,7 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>69.40000000000001</v>
+        <v>69</v>
       </c>
       <c r="M2" t="inlineStr">
         <is>
@@ -11250,7 +11214,7 @@
         <v>54.7</v>
       </c>
       <c r="R2" t="n">
-        <v>40.6</v>
+        <v>38.1</v>
       </c>
       <c r="S2" t="n">
         <v>94.90000000000001</v>
@@ -11436,12 +11400,12 @@
       </c>
       <c r="BG2" t="inlineStr">
         <is>
-          <t>In From LF</t>
+          <t>In From CF</t>
         </is>
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>62</t>
+          <t>61</t>
         </is>
       </c>
       <c r="BI2" t="inlineStr">
@@ -11506,7 +11470,7 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>58.3</v>
+        <v>59</v>
       </c>
       <c r="M3" t="inlineStr">
         <is>
@@ -11520,7 +11484,7 @@
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
+          <t>Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P3" t="n">
@@ -11533,7 +11497,7 @@
         <v>41.1</v>
       </c>
       <c r="S3" t="n">
-        <v>90.40000000000001</v>
+        <v>94.90000000000001</v>
       </c>
       <c r="T3" t="n">
         <v>80</v>
@@ -11543,39 +11507,35 @@
       </c>
       <c r="V3" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W3" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="Y3" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr"/>
       <c r="AC3" t="inlineStr">
         <is>
           <t>H:2026 P:2026/2025</t>
@@ -11790,7 +11750,7 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>57.9</v>
+        <v>58.5</v>
       </c>
       <c r="M4" t="inlineStr">
         <is>
@@ -11804,7 +11764,7 @@
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
+          <t>Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P4" t="n">
@@ -11817,7 +11777,7 @@
         <v>41.1</v>
       </c>
       <c r="S4" t="n">
-        <v>88.7</v>
+        <v>93.2</v>
       </c>
       <c r="T4" t="n">
         <v>80</v>
@@ -11827,39 +11787,35 @@
       </c>
       <c r="V4" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W4" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="Y4" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr"/>
       <c r="AC4" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -12050,7 +12006,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -12074,7 +12030,7 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>55.8</v>
+        <v>55.4</v>
       </c>
       <c r="M5" t="inlineStr">
         <is>
@@ -12098,7 +12054,7 @@
         <v>54.7</v>
       </c>
       <c r="R5" t="n">
-        <v>40.6</v>
+        <v>38.1</v>
       </c>
       <c r="S5" t="n">
         <v>96.59999999999999</v>
@@ -12284,12 +12240,12 @@
       </c>
       <c r="BG5" t="inlineStr">
         <is>
-          <t>In From LF</t>
+          <t>In From CF</t>
         </is>
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>62</t>
+          <t>61</t>
         </is>
       </c>
       <c r="BI5" t="inlineStr">
@@ -12330,7 +12286,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -12354,7 +12310,7 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>55.4</v>
+        <v>55</v>
       </c>
       <c r="M6" t="inlineStr">
         <is>
@@ -12378,7 +12334,7 @@
         <v>40.1</v>
       </c>
       <c r="R6" t="n">
-        <v>40.6</v>
+        <v>38.1</v>
       </c>
       <c r="S6" t="n">
         <v>94.90000000000001</v>
@@ -12564,12 +12520,12 @@
       </c>
       <c r="BG6" t="inlineStr">
         <is>
-          <t>In From LF</t>
+          <t>In From CF</t>
         </is>
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>62</t>
+          <t>61</t>
         </is>
       </c>
       <c r="BI6" t="inlineStr">
@@ -12610,7 +12566,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -12634,7 +12590,7 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>54.8</v>
+        <v>54.5</v>
       </c>
       <c r="M7" t="inlineStr">
         <is>
@@ -12658,7 +12614,7 @@
         <v>54.7</v>
       </c>
       <c r="R7" t="n">
-        <v>40.6</v>
+        <v>38.1</v>
       </c>
       <c r="S7" t="n">
         <v>100</v>
@@ -12844,12 +12800,12 @@
       </c>
       <c r="BG7" t="inlineStr">
         <is>
-          <t>In From LF</t>
+          <t>In From CF</t>
         </is>
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>62</t>
+          <t>61</t>
         </is>
       </c>
       <c r="BI7" t="inlineStr">
@@ -13450,7 +13406,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -13474,7 +13430,7 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>51.8</v>
+        <v>51.4</v>
       </c>
       <c r="M10" t="inlineStr">
         <is>
@@ -13498,7 +13454,7 @@
         <v>54.7</v>
       </c>
       <c r="R10" t="n">
-        <v>40.6</v>
+        <v>38.1</v>
       </c>
       <c r="S10" t="n">
         <v>86.40000000000001</v>
@@ -13684,12 +13640,12 @@
       </c>
       <c r="BG10" t="inlineStr">
         <is>
-          <t>In From LF</t>
+          <t>In From CF</t>
         </is>
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>62</t>
+          <t>61</t>
         </is>
       </c>
       <c r="BI10" t="inlineStr">
@@ -13710,7 +13666,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Luis Garcia</t>
+          <t>Luis García Jr.</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -13754,7 +13710,7 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>50.6</v>
+        <v>51.2</v>
       </c>
       <c r="M11" t="inlineStr">
         <is>
@@ -13768,7 +13724,7 @@
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
+          <t>Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P11" t="n">
@@ -13781,7 +13737,7 @@
         <v>41.1</v>
       </c>
       <c r="S11" t="n">
-        <v>92.09999999999999</v>
+        <v>96.59999999999999</v>
       </c>
       <c r="T11" t="n">
         <v>80</v>
@@ -13791,39 +13747,35 @@
       </c>
       <c r="V11" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W11" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X11" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="Y11" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr"/>
       <c r="AC11" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -14294,7 +14246,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -14318,7 +14270,7 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>49.1</v>
+        <v>48.8</v>
       </c>
       <c r="M13" t="inlineStr">
         <is>
@@ -14342,7 +14294,7 @@
         <v>54.7</v>
       </c>
       <c r="R13" t="n">
-        <v>40.6</v>
+        <v>38.1</v>
       </c>
       <c r="S13" t="n">
         <v>44.8</v>
@@ -14528,12 +14480,12 @@
       </c>
       <c r="BG13" t="inlineStr">
         <is>
-          <t>In From LF</t>
+          <t>In From CF</t>
         </is>
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>62</t>
+          <t>61</t>
         </is>
       </c>
       <c r="BI13" t="inlineStr">
@@ -14574,7 +14526,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -14598,7 +14550,7 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>48.1</v>
+        <v>47.8</v>
       </c>
       <c r="M14" t="inlineStr">
         <is>
@@ -14622,7 +14574,7 @@
         <v>40.1</v>
       </c>
       <c r="R14" t="n">
-        <v>40.6</v>
+        <v>38.1</v>
       </c>
       <c r="S14" t="n">
         <v>96.59999999999999</v>
@@ -14808,12 +14760,12 @@
       </c>
       <c r="BG14" t="inlineStr">
         <is>
-          <t>In From LF</t>
+          <t>In From CF</t>
         </is>
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>62</t>
+          <t>61</t>
         </is>
       </c>
       <c r="BI14" t="inlineStr">
@@ -14854,7 +14806,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -14878,7 +14830,7 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>47.8</v>
+        <v>47.5</v>
       </c>
       <c r="M15" t="inlineStr">
         <is>
@@ -14902,7 +14854,7 @@
         <v>54.7</v>
       </c>
       <c r="R15" t="n">
-        <v>40.6</v>
+        <v>38.1</v>
       </c>
       <c r="S15" t="n">
         <v>93.2</v>
@@ -15088,12 +15040,12 @@
       </c>
       <c r="BG15" t="inlineStr">
         <is>
-          <t>In From LF</t>
+          <t>In From CF</t>
         </is>
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>62</t>
+          <t>61</t>
         </is>
       </c>
       <c r="BI15" t="inlineStr">
@@ -15109,24 +15061,24 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>650490</t>
+          <t>665862</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Yandy Díaz</t>
+          <t>Jazz Chisholm Jr.</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
+          <t>NYY</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
           <t>TB</t>
         </is>
       </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>NYY</t>
-        </is>
-      </c>
       <c r="F16" t="inlineStr">
         <is>
           <t>2026-10-06T00:00:00Z</t>
@@ -15139,17 +15091,17 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>6</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>Cam Schlittler</t>
+          <t>Freddy Peralta</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>693645</t>
+          <t>642547</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -15158,7 +15110,7 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>46.3</v>
+        <v>46.7</v>
       </c>
       <c r="M16" t="inlineStr">
         <is>
@@ -15172,11 +15124,11 @@
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>Premium Lineup Spot</t>
+          <t>Strong Barrel, Platoon Edge</t>
         </is>
       </c>
       <c r="P16" t="n">
-        <v>41</v>
+        <v>42.2</v>
       </c>
       <c r="Q16" t="n">
         <v>33.4</v>
@@ -15185,13 +15137,13 @@
         <v>41.1</v>
       </c>
       <c r="S16" t="n">
-        <v>93.2</v>
+        <v>76.2</v>
       </c>
       <c r="T16" t="n">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="U16" t="n">
-        <v>20.9</v>
+        <v>14.6</v>
       </c>
       <c r="V16" t="inlineStr">
         <is>
@@ -15205,7 +15157,7 @@
       </c>
       <c r="X16" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>6</t>
         </is>
       </c>
       <c r="Y16" t="inlineStr">
@@ -15243,12 +15195,12 @@
       </c>
       <c r="AH16" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AI16" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>23</t>
         </is>
       </c>
       <c r="AJ16" t="inlineStr">
@@ -15258,12 +15210,12 @@
       </c>
       <c r="AK16" t="inlineStr">
         <is>
-          <t>Last 7 games: 7/27, 0 HR</t>
+          <t>Last 7 games: 5/23, 0 HR</t>
         </is>
       </c>
       <c r="AL16" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 7.6% barrel, 13.6 HR allowed</t>
+          <t>platoon edge; pitcher baseline 6.8% barrel, 22.4 HR allowed</t>
         </is>
       </c>
       <c r="AM16" t="inlineStr">
@@ -15273,97 +15225,97 @@
       </c>
       <c r="AN16" t="inlineStr">
         <is>
-          <t>7.46</t>
+          <t>10.24</t>
         </is>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
-          <t>49.42</t>
+          <t>42.95</t>
         </is>
       </c>
       <c r="AP16" t="inlineStr">
         <is>
-          <t>91.53</t>
+          <t>89.98</t>
         </is>
       </c>
       <c r="AQ16" t="inlineStr">
         <is>
-          <t>103.1694</t>
+          <t>100.4248</t>
         </is>
       </c>
       <c r="AR16" t="inlineStr">
         <is>
-          <t>0.4453</t>
+          <t>0.4005</t>
         </is>
       </c>
       <c r="AS16" t="inlineStr">
         <is>
-          <t>0.1621</t>
+          <t>0.1791</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr">
         <is>
-          <t>0.3484</t>
+          <t>0.3093</t>
         </is>
       </c>
       <c r="AU16" t="inlineStr">
         <is>
-          <t>73.5</t>
+          <t>73.2</t>
         </is>
       </c>
       <c r="AV16" t="inlineStr">
         <is>
-          <t>37.37</t>
+          <t>32.25</t>
         </is>
       </c>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>23.46</t>
+          <t>50.3</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>19.65</t>
+          <t>30.19</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr">
         <is>
-          <t>22.9</t>
+          <t>22.6</t>
         </is>
       </c>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>0.1617</t>
+          <t>0.1893</t>
         </is>
       </c>
       <c r="BA16" t="inlineStr">
         <is>
-          <t>7.57</t>
+          <t>6.85</t>
         </is>
       </c>
       <c r="BB16" t="inlineStr">
         <is>
-          <t>38.87</t>
+          <t>36.39</t>
         </is>
       </c>
       <c r="BC16" t="inlineStr">
         <is>
-          <t>88.58</t>
+          <t>87.72</t>
         </is>
       </c>
       <c r="BD16" t="inlineStr">
         <is>
-          <t>0.3434</t>
+          <t>0.368</t>
         </is>
       </c>
       <c r="BE16" t="inlineStr">
         <is>
-          <t>0.1302</t>
+          <t>0.1417</t>
         </is>
       </c>
       <c r="BF16" t="inlineStr">
         <is>
-          <t>25.76</t>
+          <t>28.41</t>
         </is>
       </c>
       <c r="BG16" t="inlineStr">
@@ -15389,12 +15341,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>665862</t>
+          <t>641355</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Jazz Chisholm</t>
+          <t>Cody Bellinger</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -15419,7 +15371,7 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -15438,7 +15390,7 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>46.1</v>
+        <v>46.4</v>
       </c>
       <c r="M17" t="inlineStr">
         <is>
@@ -15452,11 +15404,11 @@
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel, Platoon Edge</t>
+          <t>Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P17" t="n">
-        <v>42.2</v>
+        <v>30.5</v>
       </c>
       <c r="Q17" t="n">
         <v>33.4</v>
@@ -15465,49 +15417,45 @@
         <v>41.1</v>
       </c>
       <c r="S17" t="n">
-        <v>71.7</v>
+        <v>100</v>
       </c>
       <c r="T17" t="n">
         <v>80</v>
       </c>
       <c r="U17" t="n">
-        <v>14.6</v>
+        <v>18.3</v>
       </c>
       <c r="V17" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X17" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W17" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X17" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="Y17" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr"/>
       <c r="AC17" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -15527,22 +15475,22 @@
       </c>
       <c r="AH17" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AI17" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>28</t>
         </is>
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AK17" t="inlineStr">
         <is>
-          <t>Last 7 games: 5/23, 0 HR</t>
+          <t>Last 7 games: 3/28, 1 HR</t>
         </is>
       </c>
       <c r="AL17" t="inlineStr">
@@ -15557,67 +15505,67 @@
       </c>
       <c r="AN17" t="inlineStr">
         <is>
-          <t>10.24</t>
+          <t>6.87</t>
         </is>
       </c>
       <c r="AO17" t="inlineStr">
         <is>
-          <t>42.95</t>
+          <t>37.83</t>
         </is>
       </c>
       <c r="AP17" t="inlineStr">
         <is>
-          <t>89.98</t>
+          <t>88.93</t>
         </is>
       </c>
       <c r="AQ17" t="inlineStr">
         <is>
-          <t>100.4248</t>
+          <t>98.5475</t>
         </is>
       </c>
       <c r="AR17" t="inlineStr">
         <is>
-          <t>0.4005</t>
+          <t>0.4152</t>
         </is>
       </c>
       <c r="AS17" t="inlineStr">
         <is>
-          <t>0.1791</t>
+          <t>0.1505</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr">
         <is>
-          <t>0.3093</t>
+          <t>0.3314</t>
         </is>
       </c>
       <c r="AU17" t="inlineStr">
         <is>
-          <t>73.2</t>
+          <t>69.96</t>
         </is>
       </c>
       <c r="AV17" t="inlineStr">
         <is>
-          <t>32.25</t>
+          <t>4.82</t>
         </is>
       </c>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>50.3</t>
+          <t>44.36</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>30.19</t>
+          <t>31.85</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr">
         <is>
-          <t>22.6</t>
+          <t>20.6</t>
         </is>
       </c>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>0.1893</t>
+          <t>0.1779</t>
         </is>
       </c>
       <c r="BA17" t="inlineStr">
@@ -15673,27 +15621,27 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>608070</t>
+          <t>650490</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>José Ramírez</t>
+          <t>Yandy Díaz</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>CLE</t>
+          <t>TB</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>CWS</t>
+          <t>NYY</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2026-10-05T21:00:00Z</t>
+          <t>2026-10-06T00:00:00Z</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -15703,26 +15651,26 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>Anthony Kay</t>
+          <t>Cam Schlittler</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>641743</t>
+          <t>693645</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>R</t>
         </is>
       </c>
       <c r="L18" t="n">
-        <v>45.7</v>
+        <v>46.3</v>
       </c>
       <c r="M18" t="inlineStr">
         <is>
@@ -15736,26 +15684,26 @@
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>Premium Lineup Spot, Platoon Edge</t>
+          <t>Premium Lineup Spot</t>
         </is>
       </c>
       <c r="P18" t="n">
-        <v>25.8</v>
+        <v>41</v>
       </c>
       <c r="Q18" t="n">
-        <v>38.1</v>
+        <v>33.4</v>
       </c>
       <c r="R18" t="n">
-        <v>40.6</v>
+        <v>41.1</v>
       </c>
       <c r="S18" t="n">
-        <v>100</v>
+        <v>93.2</v>
       </c>
       <c r="T18" t="n">
-        <v>75</v>
+        <v>50</v>
       </c>
       <c r="U18" t="n">
-        <v>23.4</v>
+        <v>20.9</v>
       </c>
       <c r="V18" t="inlineStr">
         <is>
@@ -15769,7 +15717,7 @@
       </c>
       <c r="X18" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="Y18" t="inlineStr">
@@ -15790,7 +15738,7 @@
       <c r="AB18" t="inlineStr"/>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AD18" t="inlineStr"/>
@@ -15807,12 +15755,12 @@
       </c>
       <c r="AH18" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AI18" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>27</t>
         </is>
       </c>
       <c r="AJ18" t="inlineStr">
@@ -15822,12 +15770,12 @@
       </c>
       <c r="AK18" t="inlineStr">
         <is>
-          <t>Last 7 games: 8/29, 0 HR</t>
+          <t>Last 7 games: 7/27, 0 HR</t>
         </is>
       </c>
       <c r="AL18" t="inlineStr">
         <is>
-          <t>switch hitter; pitcher baseline 8.1% barrel, 21.0 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 7.6% barrel, 13.6 HR allowed</t>
         </is>
       </c>
       <c r="AM18" t="inlineStr">
@@ -15837,112 +15785,112 @@
       </c>
       <c r="AN18" t="inlineStr">
         <is>
-          <t>4.97</t>
+          <t>7.46</t>
         </is>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
-          <t>38.26</t>
+          <t>49.42</t>
         </is>
       </c>
       <c r="AP18" t="inlineStr">
         <is>
-          <t>88.69</t>
+          <t>91.53</t>
         </is>
       </c>
       <c r="AQ18" t="inlineStr">
         <is>
-          <t>99.2749</t>
+          <t>103.1694</t>
         </is>
       </c>
       <c r="AR18" t="inlineStr">
         <is>
-          <t>0.4075</t>
+          <t>0.4453</t>
         </is>
       </c>
       <c r="AS18" t="inlineStr">
         <is>
-          <t>0.1361</t>
+          <t>0.1621</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr">
         <is>
-          <t>0.3301</t>
+          <t>0.3484</t>
         </is>
       </c>
       <c r="AU18" t="inlineStr">
         <is>
-          <t>70.41</t>
+          <t>73.5</t>
         </is>
       </c>
       <c r="AV18" t="inlineStr">
         <is>
-          <t>12.84</t>
+          <t>37.37</t>
         </is>
       </c>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>50.41</t>
+          <t>23.46</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>27.87</t>
+          <t>19.65</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr">
         <is>
-          <t>17.4</t>
+          <t>22.9</t>
         </is>
       </c>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>0.1591</t>
+          <t>0.1617</t>
         </is>
       </c>
       <c r="BA18" t="inlineStr">
         <is>
-          <t>8.1</t>
+          <t>7.57</t>
         </is>
       </c>
       <c r="BB18" t="inlineStr">
         <is>
-          <t>38.9</t>
+          <t>38.87</t>
         </is>
       </c>
       <c r="BC18" t="inlineStr">
         <is>
-          <t>88.3</t>
+          <t>88.58</t>
         </is>
       </c>
       <c r="BD18" t="inlineStr">
         <is>
-          <t>0.419</t>
+          <t>0.3434</t>
         </is>
       </c>
       <c r="BE18" t="inlineStr">
         <is>
-          <t>0.153</t>
+          <t>0.1302</t>
         </is>
       </c>
       <c r="BF18" t="inlineStr">
         <is>
-          <t>22.0</t>
+          <t>25.76</t>
         </is>
       </c>
       <c r="BG18" t="inlineStr">
         <is>
-          <t>In From LF</t>
+          <t>None</t>
         </is>
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>62</t>
+          <t>72</t>
         </is>
       </c>
       <c r="BI18" t="inlineStr">
         <is>
-          <t>Progressive Field</t>
+          <t>Tropicana Field</t>
         </is>
       </c>
       <c r="BJ18" t="inlineStr"/>
@@ -15953,12 +15901,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>641355</t>
+          <t>663757</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Cody Bellinger</t>
+          <t>Trent Grisham</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -15983,7 +15931,7 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>7</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -16002,7 +15950,7 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>45.7</v>
+        <v>46</v>
       </c>
       <c r="M19" t="inlineStr">
         <is>
@@ -16016,11 +15964,11 @@
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot, Platoon Edge</t>
+          <t>Strong Barrel, Platoon Edge</t>
         </is>
       </c>
       <c r="P19" t="n">
-        <v>30.5</v>
+        <v>47.4</v>
       </c>
       <c r="Q19" t="n">
         <v>33.4</v>
@@ -16029,49 +15977,45 @@
         <v>41.1</v>
       </c>
       <c r="S19" t="n">
-        <v>95.5</v>
+        <v>64.3</v>
       </c>
       <c r="T19" t="n">
         <v>80</v>
       </c>
       <c r="U19" t="n">
-        <v>18.3</v>
+        <v>0</v>
       </c>
       <c r="V19" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X19" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W19" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X19" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="Y19" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z19" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB19" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr"/>
       <c r="AC19" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -16091,22 +16035,22 @@
       </c>
       <c r="AH19" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AI19" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>20</t>
         </is>
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AK19" t="inlineStr">
         <is>
-          <t>Last 7 games: 3/28, 1 HR</t>
+          <t>Last 7 games: 2/20, 0 HR</t>
         </is>
       </c>
       <c r="AL19" t="inlineStr">
@@ -16121,67 +16065,67 @@
       </c>
       <c r="AN19" t="inlineStr">
         <is>
-          <t>6.87</t>
+          <t>10.98</t>
         </is>
       </c>
       <c r="AO19" t="inlineStr">
         <is>
-          <t>37.83</t>
+          <t>45.63</t>
         </is>
       </c>
       <c r="AP19" t="inlineStr">
         <is>
-          <t>88.93</t>
+          <t>90.75</t>
         </is>
       </c>
       <c r="AQ19" t="inlineStr">
         <is>
-          <t>98.5475</t>
+          <t>100.7514</t>
         </is>
       </c>
       <c r="AR19" t="inlineStr">
         <is>
-          <t>0.4152</t>
+          <t>0.4497</t>
         </is>
       </c>
       <c r="AS19" t="inlineStr">
         <is>
-          <t>0.1505</t>
+          <t>0.2038</t>
         </is>
       </c>
       <c r="AT19" t="inlineStr">
         <is>
-          <t>0.3314</t>
+          <t>0.3469</t>
         </is>
       </c>
       <c r="AU19" t="inlineStr">
         <is>
-          <t>69.96</t>
+          <t>70.79</t>
         </is>
       </c>
       <c r="AV19" t="inlineStr">
         <is>
-          <t>4.82</t>
+          <t>9.51</t>
         </is>
       </c>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>44.36</t>
+          <t>45.42</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>31.85</t>
+          <t>31.05</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr">
         <is>
-          <t>20.6</t>
+          <t>22.8</t>
         </is>
       </c>
       <c r="AZ19" t="inlineStr">
         <is>
-          <t>0.1779</t>
+          <t>0.1975</t>
         </is>
       </c>
       <c r="BA19" t="inlineStr">
@@ -16237,56 +16181,56 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>663757</t>
+          <t>608070</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Trent Grisham</t>
+          <t>José Ramírez</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NYY</t>
+          <t>CLE</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>TB</t>
+          <t>CWS</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>2026-10-06T00:00:00Z</t>
+          <t>2026-10-05T21:00:00Z</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>Freddy Peralta</t>
+          <t>Anthony Kay</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>642547</t>
+          <t>641743</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>L</t>
         </is>
       </c>
       <c r="L20" t="n">
-        <v>45.4</v>
+        <v>45.3</v>
       </c>
       <c r="M20" t="inlineStr">
         <is>
@@ -16300,65 +16244,61 @@
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel, Platoon Edge</t>
+          <t>Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P20" t="n">
-        <v>47.4</v>
+        <v>25.8</v>
       </c>
       <c r="Q20" t="n">
-        <v>33.4</v>
+        <v>38.1</v>
       </c>
       <c r="R20" t="n">
-        <v>41.1</v>
+        <v>38.1</v>
       </c>
       <c r="S20" t="n">
-        <v>59.8</v>
+        <v>100</v>
       </c>
       <c r="T20" t="n">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="U20" t="n">
-        <v>0</v>
+        <v>23.4</v>
       </c>
       <c r="V20" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X20" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z20" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W20" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X20" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="Y20" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z20" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB20" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB20" t="inlineStr"/>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026/2025</t>
+          <t>H:2026/2025 P:2026</t>
         </is>
       </c>
       <c r="AD20" t="inlineStr"/>
@@ -16375,12 +16315,12 @@
       </c>
       <c r="AH20" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AI20" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>29</t>
         </is>
       </c>
       <c r="AJ20" t="inlineStr">
@@ -16390,12 +16330,12 @@
       </c>
       <c r="AK20" t="inlineStr">
         <is>
-          <t>Last 7 games: 2/20, 0 HR</t>
+          <t>Last 7 games: 8/29, 0 HR</t>
         </is>
       </c>
       <c r="AL20" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 6.8% barrel, 22.4 HR allowed</t>
+          <t>switch hitter; pitcher baseline 8.1% barrel, 21.0 HR allowed</t>
         </is>
       </c>
       <c r="AM20" t="inlineStr">
@@ -16405,112 +16345,112 @@
       </c>
       <c r="AN20" t="inlineStr">
         <is>
-          <t>10.98</t>
+          <t>4.97</t>
         </is>
       </c>
       <c r="AO20" t="inlineStr">
         <is>
-          <t>45.63</t>
+          <t>38.26</t>
         </is>
       </c>
       <c r="AP20" t="inlineStr">
         <is>
-          <t>90.75</t>
+          <t>88.69</t>
         </is>
       </c>
       <c r="AQ20" t="inlineStr">
         <is>
-          <t>100.7514</t>
+          <t>99.2749</t>
         </is>
       </c>
       <c r="AR20" t="inlineStr">
         <is>
-          <t>0.4497</t>
+          <t>0.4075</t>
         </is>
       </c>
       <c r="AS20" t="inlineStr">
         <is>
-          <t>0.2038</t>
+          <t>0.1361</t>
         </is>
       </c>
       <c r="AT20" t="inlineStr">
         <is>
-          <t>0.3469</t>
+          <t>0.3301</t>
         </is>
       </c>
       <c r="AU20" t="inlineStr">
         <is>
-          <t>70.79</t>
+          <t>70.41</t>
         </is>
       </c>
       <c r="AV20" t="inlineStr">
         <is>
-          <t>9.51</t>
+          <t>12.84</t>
         </is>
       </c>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>45.42</t>
+          <t>50.41</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>31.05</t>
+          <t>27.87</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr">
         <is>
-          <t>22.8</t>
+          <t>17.4</t>
         </is>
       </c>
       <c r="AZ20" t="inlineStr">
         <is>
-          <t>0.1975</t>
+          <t>0.1591</t>
         </is>
       </c>
       <c r="BA20" t="inlineStr">
         <is>
-          <t>6.85</t>
+          <t>8.1</t>
         </is>
       </c>
       <c r="BB20" t="inlineStr">
         <is>
-          <t>36.39</t>
+          <t>38.9</t>
         </is>
       </c>
       <c r="BC20" t="inlineStr">
         <is>
-          <t>87.72</t>
+          <t>88.3</t>
         </is>
       </c>
       <c r="BD20" t="inlineStr">
         <is>
-          <t>0.368</t>
+          <t>0.419</t>
         </is>
       </c>
       <c r="BE20" t="inlineStr">
         <is>
-          <t>0.1417</t>
+          <t>0.153</t>
         </is>
       </c>
       <c r="BF20" t="inlineStr">
         <is>
-          <t>28.41</t>
+          <t>22.0</t>
         </is>
       </c>
       <c r="BG20" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>In From CF</t>
         </is>
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>72</t>
+          <t>61</t>
         </is>
       </c>
       <c r="BI20" t="inlineStr">
         <is>
-          <t>Tropicana Field</t>
+          <t>Progressive Field</t>
         </is>
       </c>
       <c r="BJ20" t="inlineStr"/>
@@ -16546,7 +16486,7 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -16570,7 +16510,7 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>44.8</v>
+        <v>44.5</v>
       </c>
       <c r="M21" t="inlineStr">
         <is>
@@ -16594,7 +16534,7 @@
         <v>53.5</v>
       </c>
       <c r="R21" t="n">
-        <v>40.6</v>
+        <v>38.1</v>
       </c>
       <c r="S21" t="n">
         <v>64.3</v>
@@ -16780,12 +16720,12 @@
       </c>
       <c r="BG21" t="inlineStr">
         <is>
-          <t>In From LF</t>
+          <t>In From CF</t>
         </is>
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>62</t>
+          <t>61</t>
         </is>
       </c>
       <c r="BI21" t="inlineStr">
